--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487964_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487964_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.646</v>
+        <v>4.4631</v>
       </c>
       <c r="E2" t="n">
-        <v>1.757</v>
+        <v>1.3495</v>
       </c>
       <c r="F2" t="n">
-        <v>2.889</v>
+        <v>3.1136</v>
       </c>
       <c r="G2" t="n">
         <v>1.602</v>
@@ -610,13 +610,13 @@
         <v>0.7929</v>
       </c>
       <c r="S2" t="n">
-        <v>0.37</v>
+        <v>0.1872</v>
       </c>
       <c r="T2" t="n">
-        <v>0.18</v>
+        <v>-0.2275</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1901</v>
+        <v>0.4147</v>
       </c>
       <c r="V2" t="n">
         <v>1.8811</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TORIL RAYO</t>
+          <t>R. ALMAGRO LAZARO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8614</v>
+        <v>3.0663</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0908</v>
+        <v>1.3205</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7707</v>
+        <v>1.7457</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8053</v>
+        <v>2.0495</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0458</v>
+        <v>0.3563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7595</v>
+        <v>1.6932</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7147</v>
+        <v>1.3664</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6344</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0804</v>
+        <v>1.2857</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0905</v>
+        <v>0.6831</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4114</v>
+        <v>0.2756</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6791</v>
+        <v>0.4075</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0562</v>
+        <v>0.2239</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3671</v>
+        <v>-0.0459</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.311</v>
+        <v>0.2698</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. ALMAGRO LAZARO</t>
+          <t>A. TORIL RAYO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8064</v>
+        <v>2.5382</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1168</v>
+        <v>0.6833</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6895</v>
+        <v>1.8549</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0495</v>
+        <v>2.8053</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3563</v>
+        <v>2.0458</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6932</v>
+        <v>0.7595</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3664</v>
+        <v>1.7147</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08069999999999999</v>
+        <v>1.6344</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2857</v>
+        <v>0.0804</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6831</v>
+        <v>1.0905</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2756</v>
+        <v>0.4114</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4075</v>
+        <v>0.6791</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.036</v>
+        <v>-0.2671</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2496</v>
+        <v>-0.0403</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2136</v>
+        <v>-0.2267</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>F. JIMENEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6363</v>
+        <v>1.6411</v>
       </c>
       <c r="E5" t="n">
-        <v>0.897</v>
+        <v>-0.1295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7393</v>
+        <v>1.7706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.9909</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1703</v>
+        <v>0.4572</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3694</v>
+        <v>0.5337</v>
       </c>
       <c r="J5" t="n">
-        <v>1.479</v>
+        <v>-0.4508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9489</v>
+        <v>0.1078</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5301</v>
+        <v>-0.5586</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6781</v>
+        <v>1.4417</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2214</v>
+        <v>0.3494</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8995</v>
+        <v>1.0923</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0336</v>
+        <v>-0.2726</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1944</v>
+        <v>0.3213</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2281</v>
+        <v>-0.5939</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6036</v>
+        <v>-0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. JIMENEZ MARTINEZ</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3531</v>
+        <v>1.4117</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3332</v>
+        <v>0.897</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6863</v>
+        <v>0.5147</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9909</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4572</v>
+        <v>1.1703</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5337</v>
+        <v>-0.3694</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4508</v>
+        <v>1.479</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1078</v>
+        <v>0.9489</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5586</v>
+        <v>0.5301</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4417</v>
+        <v>-0.6781</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3494</v>
+        <v>0.2214</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0923</v>
+        <v>-0.8995</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
         <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5606</v>
+        <v>-0.191</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1176</v>
+        <v>-0.1944</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6781</v>
+        <v>0.0034</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4283</v>
+        <v>-0.4136</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5848</v>
+        <v>-0.8416</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1565</v>
+        <v>0.428</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.09180000000000001</v>
+        <v>1.552</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5261</v>
+        <v>1.1044</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.618</v>
+        <v>0.4477</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.668</v>
+        <v>0.054</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6462</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3142</v>
+        <v>-0.639</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5760999999999999</v>
+        <v>1.498</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1201</v>
+        <v>0.4114</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6962</v>
+        <v>1.0866</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5337</v>
+        <v>-0.0955</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6095</v>
+        <v>0.0955</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.191</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8701</v>
+        <v>-1.4737</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5331</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2491</v>
+        <v>-1.7885</v>
       </c>
       <c r="F8" t="n">
-        <v>0.428</v>
+        <v>1.2688</v>
       </c>
       <c r="G8" t="n">
-        <v>1.552</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1044</v>
+        <v>0.5261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4477</v>
+        <v>-0.618</v>
       </c>
       <c r="J8" t="n">
-        <v>0.054</v>
+        <v>-0.668</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6462</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.639</v>
+        <v>-1.3142</v>
       </c>
       <c r="M8" t="n">
-        <v>1.498</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4114</v>
+        <v>-0.1201</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0866</v>
+        <v>0.6962</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.503</v>
+        <v>0.4423</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.312</v>
+        <v>0.4058</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.191</v>
+        <v>0.0365</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4737</v>
+        <v>-0.8701</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4737</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5138</v>
+        <v>-1.3486</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6339</v>
+        <v>-2.3283</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1201</v>
+        <v>0.9797</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3137</v>
@@ -1156,13 +1156,13 @@
         <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2001</v>
+        <v>-0.0349</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4992</v>
+        <v>-0.1936</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2991</v>
+        <v>0.1587</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.151</v>
+        <v>-1.6064</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7693</v>
+        <v>-1.0562</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3818</v>
+        <v>-0.5502</v>
       </c>
       <c r="G10" t="n">
         <v>1.9338</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7328</v>
+        <v>-0.1882</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3103</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5775</v>
+        <v>0.409</v>
       </c>
       <c r="V10" t="n">
         <v>1.2071</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2174</v>
+        <v>-3.5522</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1447</v>
+        <v>-2.3672</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0727</v>
+        <v>-1.185</v>
       </c>
       <c r="G11" t="n">
         <v>2.7339</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8853</v>
+        <v>0.5505</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4062</v>
+        <v>0.1837</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4791</v>
+        <v>0.3668</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8811</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7391</v>
+        <v>-4.1527</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3538</v>
+        <v>-4.0481</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3853</v>
+        <v>-0.1045</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0704</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3693</v>
+        <v>-0.7829</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9984</v>
+        <v>-0.6927</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3709</v>
+        <v>-0.0901</v>
       </c>
       <c r="V12" t="n">
         <v>0.674</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7565</v>
+        <v>-5.8512</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8948</v>
+        <v>-3.7929</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8617</v>
+        <v>-2.0582</v>
       </c>
       <c r="G13" t="n">
         <v>-2.392</v>
@@ -1468,13 +1468,13 @@
         <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1752</v>
+        <v>-0.2698</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2616</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.323999999999998</v>
+        <v>-4.324000000000002</v>
       </c>
       <c r="E14" t="n">
         <v>-12.102</v>
       </c>
       <c r="F14" t="n">
-        <v>7.777900000000002</v>
+        <v>7.7781</v>
       </c>
       <c r="G14" t="n">
         <v>9.6004</v>
@@ -1525,7 +1525,7 @@
         <v>9.971000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.1889</v>
+        <v>-4.188899999999999</v>
       </c>
       <c r="M14" t="n">
         <v>3.8181</v>
@@ -1546,7 +1546,7 @@
         <v>10.9021</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6982000000000002</v>
+        <v>-0.6980999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-1.3203</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1952</v>
+        <v>5.8207</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4796</v>
+        <v>1.4983</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7155</v>
+        <v>4.3224</v>
       </c>
       <c r="G15" t="n">
         <v>2.2585</v>
@@ -1624,13 +1624,13 @@
         <v>3.568</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2438</v>
+        <v>0.3818</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4865</v>
+        <v>-0.4678</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2427</v>
+        <v>0.8496</v>
       </c>
       <c r="V15" t="n">
         <v>0.6036</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7862</v>
+        <v>3.2416</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2731</v>
+        <v>2.56</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5131</v>
+        <v>0.6815</v>
       </c>
       <c r="G16" t="n">
         <v>1.3581</v>
@@ -1702,13 +1702,13 @@
         <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6263</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0573</v>
+        <v>0.3442</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.431</v>
+        <v>-0.2625</v>
       </c>
       <c r="V16" t="n">
         <v>1.2071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6134</v>
+        <v>1.6558</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.3874</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4082</v>
+        <v>2.0432</v>
       </c>
       <c r="G17" t="n">
         <v>-2.179</v>
@@ -1780,13 +1780,13 @@
         <v>3.1716</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0173</v>
+        <v>0.0597</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3889</v>
+        <v>0.0186</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4061</v>
+        <v>0.0411</v>
       </c>
       <c r="V17" t="n">
         <v>0.6036</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2769</v>
+        <v>0.7708</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8748</v>
+        <v>-1.6897</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1517</v>
+        <v>2.4606</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1367</v>
@@ -1858,13 +1858,13 @@
         <v>3.3698</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1825</v>
+        <v>0.6765</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1676</v>
+        <v>0.3527</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0149</v>
+        <v>0.3238</v>
       </c>
       <c r="V18" t="n">
         <v>-2.1476</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>A. BUALÓ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9331</v>
+        <v>0.6027</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7778</v>
+        <v>0.6027</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8447</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0322</v>
+        <v>0.6027</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.309</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7232</v>
+        <v>0.6027</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2148</v>
+        <v>0.6027</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6891</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4744</v>
+        <v>0.6027</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.247</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9981</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2488</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1716</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.897</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8556</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0413</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BUALÓ</t>
+          <t>J. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6027</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6027</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6027</v>
+        <v>0.1358</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6027</v>
+        <v>0.1358</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6027</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6027</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.1358</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.1358</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.1358</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.1358</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANCHEZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.1032</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.6573</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.7605</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1358</v>
+        <v>-1.0322</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.309</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1358</v>
+        <v>-0.7232</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.2148</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.6891</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.4744</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1358</v>
+        <v>-2.247</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-1.9981</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1358</v>
+        <v>-0.2488</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1716</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1358</v>
+        <v>-0.1394</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.2649</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1358</v>
+        <v>0.1256</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0894</v>
+        <v>-1.3659</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4383</v>
+        <v>-2.8271</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3489</v>
+        <v>1.4612</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1856</v>
@@ -2170,13 +2170,13 @@
         <v>2.5769</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7473</v>
+        <v>-0.0238</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6312</v>
+        <v>-0.02</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1161</v>
+        <v>-0.0038</v>
       </c>
       <c r="V22" t="n">
         <v>0.2666</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6053</v>
+        <v>-1.5377</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8681</v>
+        <v>-3.0532</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2628</v>
+        <v>1.5155</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5573</v>
@@ -2248,13 +2248,13 @@
         <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6338</v>
+        <v>-0.5661</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2993</v>
+        <v>-0.4844</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3345</v>
+        <v>-0.0818</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2071</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3886</v>
+        <v>-4.7608</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9352</v>
+        <v>-5.1389</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5466</v>
+        <v>0.3781</v>
       </c>
       <c r="G24" t="n">
         <v>-5.8646</v>
@@ -2326,13 +2326,13 @@
         <v>3.568</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7357</v>
+        <v>0.3635</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1031</v>
+        <v>-0.1007</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6327</v>
+        <v>0.4642</v>
       </c>
       <c r="V24" t="n">
         <v>1.1367</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.324200000000001</v>
+        <v>4.324000000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7781</v>
+        <v>-7.778</v>
       </c>
       <c r="F25" t="n">
-        <v>12.1021</v>
+        <v>12.102</v>
       </c>
       <c r="G25" t="n">
         <v>-9.600300000000001</v>
@@ -2404,13 +2404,13 @@
         <v>22.7957</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6981000000000002</v>
+        <v>0.6980999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6223</v>
+        <v>-0.6223000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3203</v>
+        <v>1.3204</v>
       </c>
       <c r="V25" t="n">
         <v>1.333</v>
